--- a/artfynd/A 50779-2024 artfynd.xlsx
+++ b/artfynd/A 50779-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122239339</v>
       </c>
       <c r="B2" t="n">
-        <v>9384</v>
+        <v>9389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 50779-2024 artfynd.xlsx
+++ b/artfynd/A 50779-2024 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100859</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Bokoxe</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Dorcus parallelipipedus</t>
@@ -770,11 +765,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Hedbokskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>bok</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">

--- a/artfynd/A 50779-2024 artfynd.xlsx
+++ b/artfynd/A 50779-2024 artfynd.xlsx
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>100859</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bokoxe</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Dorcus parallelipipedus</t>
@@ -765,6 +770,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">

--- a/artfynd/A 50779-2024 artfynd.xlsx
+++ b/artfynd/A 50779-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122239339</v>
+        <v>129844701</v>
       </c>
       <c r="B2" t="n">
-        <v>9389</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100859</v>
+        <v>100077</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bokoxe</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dorcus parallelipipedus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,19 +704,27 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Lökeröd, träd 10301_2024, Sk</t>
+          <t>Lökaröd 6:15 där bäcken övergår i rör, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443437</v>
+        <v>443273</v>
       </c>
       <c r="R2" t="n">
-        <v>6183223</v>
+        <v>6183146</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +746,19 @@
           <t>Degeberga</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>M_Epifyter_24_10301</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår i snö, se bilder. Allra längst upp i liten bäck/öppet dike som här mynner fram ur ett täckdike. Hör via Dunderbäcken och Kölebäcken till Segeholmsåns vattensystem.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,38 +770,140 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Hedbokskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Martin Stoltze</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Martin Stoltze</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122239339</v>
+      </c>
+      <c r="B3" t="n">
+        <v>9403</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100859</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bokoxe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dorcus parallelipipedus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>N Lökeröd, träd 10301_2024, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>443437</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6183223</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Degeberga</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>M_Epifyter_24_10301</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Emma Arneng</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Emma Arneng</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>

--- a/artfynd/A 50779-2024 artfynd.xlsx
+++ b/artfynd/A 50779-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844701</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,8 +918,17 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122239339</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>